--- a/results/log_pv_cap_baseline_estimates.xlsx
+++ b/results/log_pv_cap_baseline_estimates.xlsx
@@ -413,795 +413,790 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:P17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
+          <t>baseline-ML_LagFE(SLX)-inverse_distance-Running ML_LagFE(SLX):inverse_distance for log_pv_cap ~ (baseline): ['log_income', 'log_hholds', 'irradiance']</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>baseline-ML_LagFE(SLX)-k_nearest-Running ML_LagFE(SLX):k_nearest for log_pv_cap ~ (baseline): ['log_income', 'log_hholds', 'irradiance']</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>baseline-ML_LagFE(SLX)-queen-Running ML_LagFE(SLX):queen for log_pv_cap ~ (baseline): ['log_income', 'log_hholds', 'irradiance']</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>baseline-ML_LagFE-inverse_distance-Running ML_LagFE:inverse_distance for log_pv_cap ~ (baseline): ['log_income', 'log_hholds', 'irradiance']</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>baseline-ML_LagFE-k_nearest-Running ML_LagFE:k_nearest for log_pv_cap ~ (baseline): ['log_income', 'log_hholds', 'irradiance']</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>baseline-ML_LagFE-queen-Running ML_LagFE:queen for log_pv_cap ~ (baseline): ['log_income', 'log_hholds', 'irradiance']</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>baseline-ML_ErrorFE-inverse_distance-Running ML_ErrorFE:inverse_distance for log_pv_cap ~ (baseline): ['log_income', 'log_hholds', 'irradiance']</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>baseline-ML_ErrorFE-k_nearest-Running ML_ErrorFE:k_nearest for log_pv_cap ~ (baseline): ['log_income', 'log_hholds', 'irradiance']</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>baseline-ML_ErrorFE-queen-Running ML_ErrorFE:queen for log_pv_cap ~ (baseline): ['log_income', 'log_hholds', 'irradiance']</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>baseline-PooledOLS-inverse_distance-Running PooledOLS:inverse_distance for log_pv_cap ~ (baseline): ['log_income', 'log_hholds', 'irradiance']</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>baseline-PooledOLS-k_nearest-Running PooledOLS:k_nearest for log_pv_cap ~ (baseline): ['log_income', 'log_hholds', 'irradiance']</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>baseline-PooledOLS-queen-Running PooledOLS:queen for log_pv_cap ~ (baseline): ['log_income', 'log_hholds', 'irradiance']</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>baseline-PanelRE-inverse_distance-Running PanelRE:inverse_distance for log_pv_cap ~ (baseline): ['log_income', 'log_hholds', 'irradiance']</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>baseline-PanelRE-k_nearest-Running PanelRE:k_nearest for log_pv_cap ~ (baseline): ['log_income', 'log_hholds', 'irradiance']</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>baseline-PanelRE-queen-Running PanelRE:queen for log_pv_cap ~ (baseline): ['log_income', 'log_hholds', 'irradiance']</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>baseline-ML_LagFE-inverse_distance-Running ML_LagFE:inverse_distance for log_pv_cap ~ (baseline): ['log_income', 'log_hholds', 'irradiance']</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>baseline-ML_LagFE-k_nearest-Running ML_LagFE:k_nearest for log_pv_cap ~ (baseline): ['log_income', 'log_hholds', 'irradiance']</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>baseline-ML_LagFE-queen-Running ML_LagFE:queen for log_pv_cap ~ (baseline): ['log_income', 'log_hholds', 'irradiance']</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>baseline-ML_ErrorFE-inverse_distance-Running ML_ErrorFE:inverse_distance for log_pv_cap ~ (baseline): ['log_income', 'log_hholds', 'irradiance']</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>baseline-ML_ErrorFE-k_nearest-Running ML_ErrorFE:k_nearest for log_pv_cap ~ (baseline): ['log_income', 'log_hholds', 'irradiance']</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>baseline-ML_ErrorFE-queen-Running ML_ErrorFE:queen for log_pv_cap ~ (baseline): ['log_income', 'log_hholds', 'irradiance']</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>baseline-ML_LagFE(SLX)-inverse_distance-Running ML_LagFE(SLX):inverse_distance for log_pv_cap ~ (baseline): ['log_income', 'log_hholds', 'irradiance']</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>baseline-ML_LagFE(SLX)-k_nearest-Running ML_LagFE(SLX):k_nearest for log_pv_cap ~ (baseline): ['log_income', 'log_hholds', 'irradiance']</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>baseline-ML_LagFE(SLX)-queen-Running ML_LagFE(SLX):queen for log_pv_cap ~ (baseline): ['log_income', 'log_hholds', 'irradiance']</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CONSTANT</t>
+          <t>log_income</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.828***</t>
+          <t>-0.512*</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.828***</t>
+          <t>-0.061</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.828***</t>
+          <t>0.090</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-13.033***</t>
+          <t>-0.382**</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-13.033***</t>
+          <t>2.057***</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-13.033***</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+          <t>2.824***</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-0.426+</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2.593***</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>3.404***</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>-0.742***</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-0.742***</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>-0.742***</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>3.117***</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>3.117***</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>3.117***</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>log_income</t>
+          <t>log_hholds</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-0.742***</t>
+          <t>0.273***</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.742***</t>
+          <t>0.271***</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-0.742***</t>
+          <t>0.271***</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3.117***</t>
+          <t>0.270***</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>3.117***</t>
+          <t>0.273***</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3.117***</t>
+          <t>0.273***</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.501***</t>
+          <t>0.274***</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.989***</t>
+          <t>0.277***</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2.722***</t>
+          <t>0.276***</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-0.601**</t>
+          <t>0.253***</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2.103***</t>
+          <t>0.253***</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>3.231***</t>
+          <t>0.253***</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>-0.679**</t>
+          <t>0.281***</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-0.221</t>
+          <t>0.281***</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>0.281***</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>log_hholds</t>
+          <t>W_log_income</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.253***</t>
+          <t>1.553***</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.253***</t>
+          <t>2.753***</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.253***</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0.281***</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0.281***</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0.281***</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.274***</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.277***</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.277***</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.278***</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>0.280***</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0.279***</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0.278***</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0.276***</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0.276***</t>
-        </is>
-      </c>
+          <t>3.202***</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>irradiance</t>
+          <t>W_log_hholds</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.001***</t>
+          <t>-0.271***</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.001***</t>
+          <t>-0.133***</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.001***</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>-0.000</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>-0.000</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>-0.000</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-203344648.773</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-3752132061.852</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-2582312040.694</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>-611705990.759</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-7416957898.746</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>-1892515328.595</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>205253449.514</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>-6440356316.203</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>-1825828723.661</t>
-        </is>
-      </c>
+          <t>-0.082***</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>r2</t>
+          <t>W_log_pv_cap</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.258</t>
+          <t>0.830***</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.258</t>
+          <t>0.405***</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.258</t>
+          <t>0.244***</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>0.812***</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>0.346***</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.069</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.800</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.771</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0.760</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0.543</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>0.723</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>0.745</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0.809</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0.795</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0.789</t>
-        </is>
-      </c>
+          <t>0.186***</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>llr</t>
+          <t>r2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-1815.563</t>
+          <t>0.802</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1815.563</t>
+          <t>0.785</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-1815.563</t>
+          <t>0.777</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-2497.776</t>
+          <t>0.794</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-2497.776</t>
+          <t>0.765</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-2497.776</t>
+          <t>0.754</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2201.181</t>
+          <t>0.548</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1998.947</t>
+          <t>0.730</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1943.002</t>
+          <t>0.741</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2249.674</t>
+          <t>0.258</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2010.909</t>
+          <t>0.258</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1949.485</t>
+          <t>0.258</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2262.191</t>
+          <t>0.069</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2145.670</t>
+          <t>0.069</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2105.392</t>
+          <t>0.069</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>aic</t>
+          <t>llr</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3639.125</t>
+          <t>2247.213</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3639.125</t>
+          <t>2119.046</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3639.125</t>
+          <t>2078.550</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5003.552</t>
+          <t>2193.659</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5003.552</t>
+          <t>2001.178</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>5003.552</t>
+          <t>1943.411</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4394.362</t>
+          <t>2233.616</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3989.893</t>
+          <t>1994.054</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-3878.005</t>
+          <t>1934.416</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-4493.349</t>
+          <t>-1815.563</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-4015.819</t>
+          <t>-1815.563</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-3892.969</t>
+          <t>-1815.563</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>-4510.382</t>
+          <t>-2497.776</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-4277.339</t>
+          <t>-2497.776</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>-4196.784</t>
+          <t>-2497.776</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>schwarz</t>
+          <t>aic</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3662.920</t>
+          <t>-4484.427</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3662.920</t>
+          <t>-4228.092</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3662.920</t>
+          <t>-4147.100</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>5027.347</t>
+          <t>-4381.318</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5027.347</t>
+          <t>-3996.357</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>5027.347</t>
+          <t>-3880.823</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4370.567</t>
+          <t>-4463.232</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3966.098</t>
+          <t>-3984.108</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-3854.210</t>
+          <t>-3864.833</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-4475.503</t>
+          <t>3639.125</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-3997.973</t>
+          <t>3639.125</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-3875.123</t>
+          <t>3639.125</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-4468.741</t>
+          <t>5003.552</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-4235.698</t>
+          <t>5003.552</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>-4155.143</t>
+          <t>5003.552</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>n_obs</t>
+          <t>schwarz</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2832</t>
+          <t>-4454.627</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2832</t>
+          <t>-4198.292</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2832</t>
+          <t>-4117.301</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2832</t>
+          <t>-4363.438</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2832</t>
+          <t>-3978.477</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2832</t>
+          <t>-3862.943</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2832</t>
+          <t>-4451.312</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2832</t>
+          <t>-3972.188</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2832</t>
+          <t>-3852.913</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2832</t>
+          <t>3662.920</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2832</t>
+          <t>3662.920</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2832</t>
+          <t>3662.920</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2832</t>
+          <t>5027.347</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2832</t>
+          <t>5027.347</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2832</t>
+          <t>5027.347</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>n_obs</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2864</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2864</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2864</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2864</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2864</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2864</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2864</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2864</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2864</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2832</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2832</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2832</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2832</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2832</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2832</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>tests</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
         <is>
           <t xml:space="preserve">                        Test    Statistic  df  p-value
 0       LM Marginal RE (LM1)    83.300664   1      0.0
@@ -1209,7 +1204,7 @@
 2             LM Joint (LMJ)  8546.350065   2      0.0</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t xml:space="preserve">                        Test    Statistic  df  p-value
 0       LM Marginal RE (LM1)    83.300664   1      0.0
@@ -1217,7 +1212,7 @@
 2             LM Joint (LMJ)  7093.049921   2      0.0</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">                        Test    Statistic  df  p-value
 0       LM Marginal RE (LM1)    83.300664   1      0.0
@@ -1225,44 +1220,113 @@
 2             LM Joint (LMJ)  7014.043156   2      0.0</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t xml:space="preserve">                         Test    Statistic df p-value
 0      LM Conditional Spatial    80.478379  1     0.0
 1  Hausman Specification Test  1240.433369  2     0.0</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t xml:space="preserve">                         Test    Statistic df p-value
 0      LM Conditional Spatial    20.926604  1     0.0
 1  Hausman Specification Test  1240.433369  2     0.0</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t xml:space="preserve">                         Test    Statistic df p-value
 0      LM Conditional Spatial    14.748114  1     0.0
 1  Hausman Specification Test  1240.433369  2     0.0</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>outputs</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      var_names coefficients   std_err    zt_stat      prob
+0    log_income    -0.512224  0.229948  -2.227565   0.02591
+1    log_hholds     0.273361   0.00342   79.93929       0.0
+2  W_log_income     1.553016  0.362068   4.289296  0.000018
+3  W_log_hholds    -0.271432  0.026118 -10.392664       0.0
+4  W_log_pv_cap     0.829616  0.039506  20.999908       0.0</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      var_names coefficients   std_err    zt_stat      prob
+0    log_income    -0.060869  0.227634  -0.267399  0.789162
+1    log_hholds     0.271348  0.003542  76.614827       0.0
+2  W_log_income      2.75284  0.271293  10.147123       0.0
+3  W_log_hholds    -0.133481  0.012353 -10.805216       0.0
+4  W_log_pv_cap     0.405043  0.029025  13.954931       0.0</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      var_names coefficients   std_err    zt_stat      prob
+0    log_income     0.089529  0.223001   0.401473  0.688072
+1    log_hholds     0.271212  0.003601  75.319208       0.0
+2  W_log_income     3.201578  0.246581  12.983855       0.0
+3  W_log_hholds    -0.082153  0.009535  -8.616152       0.0
+4  W_log_pv_cap     0.243883  0.025331   9.627707       0.0</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      var_names coefficients   std_err    zt_stat     prob
+0    log_income    -0.382483  0.121946  -3.136489  0.00171
+1    log_hholds     0.269618  0.003484  77.377498      0.0
+2  W_log_pv_cap     0.811904  0.017465  46.488389      0.0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      var_names coefficients   std_err    zt_stat prob
+0    log_income     2.056976  0.124882   16.47131  0.0
+1    log_hholds     0.273102   0.00371  73.607436  0.0
+2  W_log_pv_cap     0.346284  0.019739  17.542973  0.0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      var_names coefficients   std_err    zt_stat prob
+0    log_income     2.823851  0.119566  23.617506  0.0
+1    log_hholds       0.2731  0.003788  72.093839  0.0
+2  W_log_pv_cap     0.186302  0.016931  11.003299  0.0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    var_names coefficients   std_err    zt_stat      prob
+0  log_income    -0.426158  0.228204  -1.867446  0.061839
+1  log_hholds     0.273548  0.003422  79.944689       0.0
+2      lambda     0.954346  0.010992  86.824504       0.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    var_names coefficients   std_err    zt_stat prob
+0  log_income     2.592853  0.149058  17.394958  0.0
+1  log_hholds       0.2766  0.003608  76.654703  0.0
+2      lambda     0.516133  0.025478  20.257842  0.0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    var_names coefficients   std_err    zt_stat prob
+0  log_income     3.403766  0.113522  29.983273  0.0
+1  log_hholds     0.275667  0.003752    73.4787  0.0
+2      lambda     0.248961   0.02548   9.770753  0.0</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t xml:space="preserve">    var_names coefficients   std_err    zt_stat      prob
 0    CONSTANT     1.827545  0.371875   4.914412  0.000001
@@ -1271,7 +1335,7 @@
 3  irradiance     0.001115  0.000097  11.511499       0.0</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve">    var_names coefficients   std_err    zt_stat      prob
 0    CONSTANT     1.827545  0.371875   4.914412  0.000001
@@ -1280,7 +1344,7 @@
 3  irradiance     0.001115  0.000097  11.511499       0.0</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">    var_names coefficients   std_err    zt_stat      prob
 0    CONSTANT     1.827545  0.371875   4.914412  0.000001
@@ -1289,7 +1353,7 @@
 3  irradiance     0.001115  0.000097  11.511499       0.0</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t xml:space="preserve">    var_names coefficients   std_err    zt_stat      prob
 0    CONSTANT   -13.032525  0.477159 -27.312749       0.0
@@ -1298,7 +1362,7 @@
 3  irradiance    -0.000388   0.00025  -1.554821  0.119989</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t xml:space="preserve">    var_names coefficients   std_err    zt_stat      prob
 0    CONSTANT   -13.032525  0.477159 -27.312749       0.0
@@ -1307,7 +1371,7 @@
 3  irradiance    -0.000388   0.00025  -1.554821  0.119989</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t xml:space="preserve">    var_names coefficients   std_err    zt_stat      prob
 0    CONSTANT   -13.032525  0.477159 -27.312749       0.0
@@ -1316,234 +1380,85 @@
 3  irradiance    -0.000388   0.00025  -1.554821  0.119989</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      var_names      coefficients   std_err    zt_stat  prob
-0    log_income         -0.501176  0.082236  -6.094374   0.0
-1    log_hholds          0.273671  0.003456  79.178146   0.0
-2    irradiance -203344648.772577      None       None  None
-3  W_log_pv_cap            0.8279      None       None  None</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      var_names       coefficients   std_err    zt_stat  prob
-0    log_income           1.989284  0.088102  22.579251   0.0
-1    log_hholds           0.276609  0.003703  74.699171   0.0
-2    irradiance -3752132061.852092      None       None  None
-3  W_log_pv_cap           0.344095      None       None  None</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      var_names       coefficients   std_err    zt_stat  prob
-0    log_income           2.722196  0.090145  30.197951   0.0
-1    log_hholds           0.277357  0.003789  73.203891   0.0
-2    irradiance -2582312040.693955      None       None  None
-3  W_log_pv_cap           0.188462      None       None  None</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    var_names      coefficients             std_err    zt_stat      prob
-0  log_income         -0.601248            0.227679  -2.640771  0.008272
-1  log_hholds          0.277914            0.003406  81.593267       0.0
-2  irradiance -611705990.758954  18745866354.270123  -0.032632  0.973968
-3      lambda          0.956415            0.010526  90.862974       0.0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    var_names       coefficients             std_err    zt_stat      prob
-0  log_income            2.10279            0.159999  13.142508       0.0
-1  log_hholds           0.280087            0.003552  78.855436       0.0
-2  irradiance -7416957898.745965  19837249168.919418   -0.37389  0.708486
-3      lambda           0.587728            0.022761  25.821282       0.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    var_names       coefficients             std_err    zt_stat      prob
-0  log_income           3.230701            0.119987   26.92547       0.0
-1  log_hholds           0.279175            0.003683   75.79461       0.0
-2  irradiance -1892515328.595207  20742415413.650303  -0.091239  0.927303
-3      lambda           0.315172            0.024572  12.826254       0.0</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      var_names      coefficients             std_err    zt_stat      prob
-0    log_income         -0.678811             0.22927  -2.960745  0.003069
-1    log_hholds          0.277637            0.003405  81.526882       0.0
-2    irradiance  205253449.514276  13634729557.476789   0.015054  0.987989
-3  W_log_income          1.613503             0.27878   5.787726       0.0
-4  W_log_hholds         -0.273319            0.024466 -11.171333       0.0
-5  W_irradiance -803209389.333742  13651601303.087477  -0.058836  0.953083
-6  W_log_pv_cap          0.843925                None       None      None</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      var_names       coefficients             std_err    zt_stat      prob
-0    log_income          -0.220739            0.220175  -1.002565  0.316071
-1    log_hholds           0.276061            0.003502  78.822856       0.0
-2    irradiance -6440356316.203465  13705048315.336826  -0.469926  0.638408
-3  W_log_income           2.820349            0.240368  11.733468       0.0
-4  W_log_hholds          -0.150524            0.009361 -16.080246       0.0
-5  W_irradiance  9448090558.959223  13718159265.562777   0.688729  0.490994
-6  W_log_pv_cap           0.437513                None       None      None</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      var_names        coefficients            std_err    zt_stat      prob
-0    log_income            0.017564            0.21466   0.081825  0.934786
-1    log_hholds            0.275606           0.003557  77.481589       0.0
-2    irradiance   -1825828723.66131  13693952631.95298  -0.133331  0.893932
-3  W_log_income            3.097094           0.228757  13.538822       0.0
-4  W_log_hholds           -0.105337           0.006208 -16.967789       0.0
-5  W_irradiance  14049665586.372852  13636114669.18371   1.030328  0.302856
-6  W_log_pv_cap            0.309847               None       None      None</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>effects</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            total_ML_LagFE_inverse_distance  direct_ML_LagFE_inverse_distance  \
-log_income                    -2.912130e+00                     -5.011762e-01   
-log_hholds                     1.590192e+00                      2.736713e-01   
-irradiance                    -1.181552e+09                     -2.033446e+08   
-            indirect_ML_LagFE_inverse_distance  
-log_income                       -2.410953e+00  
-log_hholds                        1.316521e+00  
-irradiance                       -9.782078e+08  </t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            total_ML_LagFE_k_nearest  direct_ML_LagFE_k_nearest  \
-log_income              3.032883e+00               1.989284e+00   
-log_hholds              4.217203e-01               2.766086e-01   
-irradiance             -5.720540e+09              -3.752132e+09   
-            indirect_ML_LagFE_k_nearest  
-log_income                 1.043599e+00  
-log_hholds                 1.451117e-01  
-irradiance                -1.968408e+09  </t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            total_ML_LagFE_queen  direct_ML_LagFE_queen  \
-log_income          3.354367e+00           2.722196e+00   
-log_hholds          3.417668e-01           2.773567e-01   
-irradiance         -3.181998e+09          -2.582312e+09   
-            indirect_ML_LagFE_queen  
-log_income             6.321711e-01  
-log_hholds             6.441009e-02  
-irradiance            -5.996861e+08  </t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            total_ML_LagFE(SLX)_inverse_distance  \
-log_income                          5.988720e+00   
-log_hholds                          2.766631e-02   
-irradiance                         -3.831198e+09   
-            direct_ML_LagFE(SLX)_inverse_distance  \
-log_income                          -6.788110e-01   
-log_hholds                           2.776369e-01   
-irradiance                           2.052534e+08   
-            indirect_ML_LagFE(SLX)_inverse_distance  
-log_income                             6.667531e+00  
-log_hholds                            -2.499706e-01  
-irradiance                            -4.036451e+09  </t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            total_ML_LagFE(SLX)_k_nearest  direct_ML_LagFE(SLX)_k_nearest  \
-log_income                   4.621634e+00                   -2.207395e-01   
-log_hholds                   2.231816e-01                    2.760613e-01   
-irradiance                   5.347204e+09                   -6.440356e+09   
-            indirect_ML_LagFE(SLX)_k_nearest  
-log_income                      4.842373e+00  
-log_hholds                     -5.287967e-02  
-irradiance                      1.178756e+10  </t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            total_ML_LagFE(SLX)_queen  direct_ML_LagFE(SLX)_queen  \
-log_income               4.512997e+00                1.756443e-02   
-log_hholds               2.467115e-01                2.756059e-01   
-irradiance               1.771178e+10               -1.825829e+09   
-            indirect_ML_LagFE(SLX)_queen  
-log_income                  4.495432e+00  
-log_hholds                 -2.889445e-02  
-irradiance                  1.953760e+10  </t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>W_log_pv_cap</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0.828</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>0.344</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>0.188</t>
-        </is>
-      </c>
+          <t>effects</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            total_ML_LagFE(SLX)_inverse_distance  \
+log_income                              6.108524   
+log_hholds                              0.011320   
+            direct_ML_LagFE(SLX)_inverse_distance  \
+log_income                              -0.512224   
+log_hholds                               0.273361   
+            indirect_ML_LagFE(SLX)_inverse_distance  
+log_income                                 6.620748  
+log_hholds                                -0.262041  </t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            total_ML_LagFE(SLX)_k_nearest  direct_ML_LagFE(SLX)_k_nearest  \
+log_income                       4.524648                       -0.060869   
+log_hholds                       0.231725                        0.271348   
+            indirect_ML_LagFE(SLX)_k_nearest  
+log_income                          4.585517  
+log_hholds                         -0.039623  </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            total_ML_LagFE(SLX)_queen  direct_ML_LagFE(SLX)_queen  \
+log_income                   4.352644                    0.089529   
+log_hholds                   0.250040                    0.271212   
+            indirect_ML_LagFE(SLX)_queen  
+log_income                      4.263115  
+log_hholds                     -0.021172  </t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            total_ML_LagFE_inverse_distance  direct_ML_LagFE_inverse_distance  \
+log_income                        -2.033449                         -0.382483   
+log_hholds                         1.433407                          0.269618   
+            indirect_ML_LagFE_inverse_distance  
+log_income                           -1.650966  
+log_hholds                            1.163789  </t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            total_ML_LagFE_k_nearest  direct_ML_LagFE_k_nearest  \
+log_income                  3.146587                   2.056976   
+log_hholds                  0.417768                   0.273102   
+            indirect_ML_LagFE_k_nearest  
+log_income                     1.089612  
+log_hholds                     0.144666  </t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            total_ML_LagFE_queen  direct_ML_LagFE_queen  \
+log_income              3.470391               2.823851   
+log_hholds              0.335628               0.273100   
+            indirect_ML_LagFE_queen  
+log_income                 0.646540  
+log_hholds                 0.062528  </t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>0.844</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>0.438</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>0.310</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1557,24 +1472,24 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0.956***</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>0.588***</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>0.315***</t>
-        </is>
-      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0.954***</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0.516***</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.249***</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
@@ -1582,7 +1497,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>W_log_income</t>
+          <t>CONSTANT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -1594,29 +1509,41 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>1.828***</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>1.828***</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>1.828***</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>1.614***</t>
+          <t>-13.033***</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2.820***</t>
+          <t>-13.033***</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>3.097***</t>
+          <t>-13.033***</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>W_log_hholds</t>
+          <t>irradiance</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -1628,56 +1555,34 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0.001***</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0.001***</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>0.001***</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>-0.273***</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>-0.151***</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>-0.105***</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>W_irradiance</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>-803209389.334</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>9448090558.959</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>14049665586.373</t>
+          <t>-0.000</t>
         </is>
       </c>
     </row>
